--- a/Unsorted/Павловск/разрушения/павловск_разрушение_подписи.xlsx
+++ b/Unsorted/Павловск/разрушения/павловск_разрушение_подписи.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Лист1" sheetId="3" r:id="rId2"/>
-    <sheet name="Лист2" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>подпись</t>
   </si>
@@ -33,12 +32,6 @@
   </si>
   <si>
     <t>подзаголовок</t>
-  </si>
-  <si>
-    <t>Вид на крепость «Мариенталь» (Бип). (Архитектор В. Бренна, 1795 - 1797 гг.). 1959 г., г. Павловск</t>
-  </si>
-  <si>
-    <t>02 ЦГАКФФД СПб Ар189563</t>
   </si>
   <si>
     <t xml:space="preserve">Великая Отечественная войны. Ансамбль Павловского дворца и парка. Разрушенный артиллерийскими снарядами фасад тронного зала дворца. 1944 г., г. Павловск
@@ -50,12 +43,6 @@
     <t>ЦГАКФФД СПб Ар189503</t>
   </si>
   <si>
-    <t xml:space="preserve">Разрушения Павловского дворца. 1944 г., г. Павловск
-Автор съемки: Величко М.А
-ЦГАКФФД СПб. Оп. 1АР-147. Ед.хр.194381
-</t>
-  </si>
-  <si>
     <t>ЦГАКФФД СПб Ар194381</t>
   </si>
   <si>
@@ -68,19 +55,7 @@
     <t>ЦГАКФФД СПб Бр64047</t>
   </si>
   <si>
-    <t xml:space="preserve">Вид печи в разрушенном зале Войны и Мира Павловского дворца.1944 г., г. Павловск
-Автор съемки: Величко Михаил Антонович
-ЦГАКФФД СПб. Оп. 1БР-54. Ед.хр.65081
-</t>
-  </si>
-  <si>
     <t>ЦГАКФФД СПб Бр65081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Внешний вид разрушенного дворца. 1944 г. г. Павловск
-Автор съемки не установлено
-ЦГАКФФД СПб. Оп. 1ВР-2. Ед.хр. 805
-</t>
   </si>
   <si>
     <t>ЦГАКФФД СПб Вр805</t>
@@ -100,73 +75,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Вид полуразрушенного Круглого зала в районе Павловского парка - Большая звезда (бывший Музыкальный павильон, архитекторы Ч.Камерон, В.Бренна. 1799-1800 гг.). Март1958 г., г. Павловск
-Автор съемки: Овчинников Кирилл Владимирович
-ЦГАКФФД СПб. Оп. 1АР-157. Ед.хр.225052
-</t>
-  </si>
-  <si>
-    <t>ЦГАКФФД СПб Ар225052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вид Висконтиева моста, взорванного фашистами при отступлении.1944 г., г. Павловск
-Автор съемки: Величко Михаил Антонович
-ЦГАКФФД СПб. Оп. 1БР-54. Ед.хр.65090
-</t>
-  </si>
-  <si>
-    <t>ЦГАКФФД СПб Бр65090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вид полуразрушенных Пиль-башни и моста.1944 г., г. ПавловскАвтор съемки: Величко Михаил Антонович
-ЦГАКФФД СПб. Оп. 1БР-54. Ед.хр.65095
-</t>
-  </si>
-  <si>
-    <t>ЦГАКФФД СПб Бр65095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Акт об утрате памятника великой княжне Александре Павловне в Павловском парке. 17 мая 1945 г.
-КГИОП. П. 246. П-1126. Л 137
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Павловский дворец. Фрагмент правого крыла с разрушениями. 1946 г.
-Автор съемки: неизвестен
-КГИОП.№ 19514
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Павловский дворец. Фрагмент левого крыла с разрушениями. 1946 г.
-Автор съемки: неизвестен
-КГИОП.№ 19510
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Павловский дворец. Разрушенные перекрытия. 1945 г
-Автор съемки: неизвестен
-КГИОП.№ 65330
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Павловский дворец. Разрушения со стороны собственного садика. 1944 г.
-Автор съемки: А.К. Сидава
-КГИОП.№ 12938
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Павловский дворец. Разбор завалов в одном из корпусов. 1945 г.
-Автор съемки: Цильке С.Г.
-КГИОП.№ 16275
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Павловский дворец. Общий вид со стороны площади строителей. 1945 г.
-Автор съемки: неизвестен
-КГИОП.№16269
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Павловский дворец. Общий вид разрушений. 1945 г.
 Автор съемки: неизвестен
 КГИОП. № 65331
@@ -203,64 +111,115 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Павловский дворец после разрушений 1940-х годов. Вид на центральный корпус и тронный зал. 25.05.1957 г. ФотолабораторияАПУ
+    <t>Павловский дворец. Разрушенные перекрытия, 1945 г Фотограф неизвестен № 65330</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Разрушения со стороны собственного садика, 1944 г. А.К. Сидава № 12938</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Разбор завалов в одном из корпусов, 1945 г Цильке С.Г. № 16275</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Общий вид разрушений, 1945 г. Фотограф неизвестен № 65331</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Общий вид правого крыла, 1944 г Фотограф неизвестен</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Нижний вестибюль, 1944 г. Григорьев А. № 14448</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Главный фасад, 1944 г. А. Григорьев № 14443</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Арматура в полукруглой нише на фасаде, 1947 Григорьев А. №19144</t>
+  </si>
+  <si>
+    <t>Павловский дворец. Музейные ценности, брошенные оккупантами под мостом у одного из корпусов дворца. 1944 г.</t>
+  </si>
+  <si>
+    <t>КГИОП. П. 246-1. П-1125. Л. 98</t>
+  </si>
+  <si>
+    <t>КГИОП. №16269</t>
+  </si>
+  <si>
+    <t>КГИОП.№ 19514</t>
+  </si>
+  <si>
+    <t>КГИОП. №55137</t>
+  </si>
+  <si>
+    <t>КГИОП.№ 19510</t>
+  </si>
+  <si>
+    <t>Большой дворец</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разрушения Павловского дворца. 1944 г., г. Павловск
+Автор съемки: Величко М.А.
+ЦГАКФФД СПб. Оп. 1АР-147. Ед.хр.194381
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вид печи в разрушенном зале Войны и Мира Павловского дворца. 1944 г., г. Павловск
+Автор съемки: Величко Михаил Антонович
+ЦГАКФФД СПб. Оп. 1БР-54. Ед.хр.65081
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Внешний вид разрушенного дворца. 1944 г., г. Павловск
+Автор съемки не установлено
+ЦГАКФФД СПб. Оп. 1ВР-2. Ед.хр. 805
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Фрагмент правого крыла с разрушениями. 1946 г.
+Автор съемки: неизвестен
+КГИОП. № 19514
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Фрагмент левого крыла с разрушениями. 1946 г.
+Автор съемки: неизвестен
+КГИОП. № 19510
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Разрушенные перекрытия. 1945 г.
+Автор съемки: неизвестен
+КГИОП. № 65330
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Разрушения со стороны собственного садика. 1944 г.
+Автор съемки: А.К. Сидава
+КГИОП. № 12938
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Разбор завалов в одном из корпусов. 1945 г.
+Автор съемки: Цильке С.Г.
+КГИОП. № 16275
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Общий вид со стороны площади строителей. 1945 г.
+Автор съемки: неизвестен
+КГИОП. № 16269
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец после разрушений 1940-х годов. Вид на центральный корпус и тронный зал. 25.05.1957 г. Фотолаборатория АПУ
 КГИОП. №55137
 </t>
-  </si>
-  <si>
-    <t>Павловский дворец. Разрушенные перекрытия, 1945 г Фотограф неизвестен № 65330</t>
-  </si>
-  <si>
-    <t>Павловский дворец. Разрушения со стороны собственного садика, 1944 г. А.К. Сидава № 12938</t>
-  </si>
-  <si>
-    <t>Павловский дворец. Разбор завалов в одном из корпусов, 1945 г Цильке С.Г. № 16275</t>
-  </si>
-  <si>
-    <t>Павловский дворец. Общий вид разрушений, 1945 г. Фотограф неизвестен № 65331</t>
-  </si>
-  <si>
-    <t>Павловский дворец. Общий вид правого крыла, 1944 г Фотограф неизвестен</t>
-  </si>
-  <si>
-    <t>Павловский дворец. Нижний вестибюль, 1944 г. Григорьев А. № 14448</t>
-  </si>
-  <si>
-    <t>Павловский дворец. Главный фасад, 1944 г. А. Григорьев № 14443</t>
-  </si>
-  <si>
-    <t>Павловский дворец. Арматура в полукруглой нише на фасаде, 1947 Григорьев А. №19144</t>
-  </si>
-  <si>
-    <t>Павловский дворец. Музейные ценности, брошенные оккупантами под мостом у одного из корпусов дворца. 1944 г.</t>
-  </si>
-  <si>
-    <t>КГИОП. П. 246. П-1126. Л 137</t>
-  </si>
-  <si>
-    <t>КГИОП. П. 246-1. П-1125. Л. 98</t>
-  </si>
-  <si>
-    <t>КГИОП. №16269</t>
-  </si>
-  <si>
-    <t>КГИОП.№ 19514</t>
-  </si>
-  <si>
-    <t>КГИОП. №55137</t>
-  </si>
-  <si>
-    <t>КГИОП.№ 19510</t>
-  </si>
-  <si>
-    <t>Большой дворец</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -286,6 +245,12 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -301,7 +266,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -309,11 +274,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -329,6 +309,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -601,7 +587,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -609,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="40.3671875" customWidth="1"/>
@@ -626,7 +612,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="5" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -640,198 +626,166 @@
     </row>
     <row r="4" spans="1:3" ht="86.4">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" spans="1:3" ht="57.6">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" spans="1:3" ht="72">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="6"/>
-    </row>
-    <row r="5" spans="1:3" ht="28.8">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="6"/>
-    </row>
-    <row r="6" spans="1:3" ht="57.6">
-      <c r="A6" t="s">
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:3" ht="72">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="6"/>
-    </row>
-    <row r="7" spans="1:3" ht="86.4">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C7" s="6"/>
     </row>
-    <row r="8" spans="1:3" ht="72">
+    <row r="8" spans="1:3" ht="57.6">
       <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="C8" s="6"/>
     </row>
     <row r="9" spans="1:3" ht="72">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6"/>
     </row>
     <row r="10" spans="1:3" ht="72">
       <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="57.6">
+    <row r="11" spans="1:3" ht="72">
       <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="C11" s="6"/>
     </row>
     <row r="12" spans="1:3" ht="57.6">
       <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:3" ht="72">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C13" s="6"/>
     </row>
-    <row r="14" spans="1:3" ht="72">
+    <row r="14" spans="1:3" ht="57.6">
       <c r="A14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C14" s="6"/>
     </row>
     <row r="15" spans="1:3" ht="72">
       <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="C15" s="6"/>
     </row>
     <row r="16" spans="1:3" ht="57.6">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="72">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="57.6">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="57.6">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="72">
       <c r="A19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="57.6">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="72">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="72">
+      <c r="A22" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="57.6">
-      <c r="A21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="57.6">
-      <c r="A22" t="s">
+      <c r="B22" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="72">
-      <c r="A23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="57.6">
-      <c r="A24" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="72">
-      <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="72">
-      <c r="A26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -859,7 +813,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -873,54 +827,10 @@
     </row>
     <row r="4" spans="1:2" ht="100.8">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="40.3671875" customWidth="1"/>
-    <col min="2" max="2" width="58.7890625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15.6">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="57.6">
-      <c r="A4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Unsorted/Павловск/разрушения/павловск_разрушение_подписи.xlsx
+++ b/Unsorted/Павловск/разрушения/павловск_разрушение_подписи.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="74">
   <si>
     <t>подпись</t>
   </si>
@@ -212,6 +212,132 @@
   <si>
     <t xml:space="preserve">Павловский дворец после разрушений 1940-х годов. Вид на центральный корпус и тронный зал. 25.05.1957 г. Фотолаборатория АПУ
 КГИОП. №55137
+</t>
+  </si>
+  <si>
+    <t>1. Павловский дворец Греческий зал. 1944 г.</t>
+  </si>
+  <si>
+    <t>2. Павловский дворец Галерея Гонзаго. 1944 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Тронный зал. 1944 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>3. Павловский дворец Галерея Гонзаго. 1944 г (1)</t>
+  </si>
+  <si>
+    <t>4. Павловский дворец Галерея Гонзаго. 1944 г (2)</t>
+  </si>
+  <si>
+    <t>5. Павловский дворец. Тронный зал. 1944 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Олейник Ф.Ф.
+Павловский дворец. Разрушенный Тронный зал
+НВК-12518
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>6. Олейник Ф.Ф. Павловский дворец. Разрушенный Тронный зал. НВК-12518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Разрушенный Итальянский зал. 1944 г. Фрагмент
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>7. Павловский дворец. Разрушенный Итальянский зал (фрагмент). 1944 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бернштейн Э.Б.
+Автолитография. Темная Буфетная и Итальянский зал в 1944 г.
+НВК-10251
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>8. Бернштейн Э.Б. Автолитография. Темная Буфетная и Итальянский зал в 1944 г. НВК-10251</t>
+  </si>
+  <si>
+    <t>9. Павловский дворец Белая столовая (Столовая Камерона). 1947 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Белая столовая (Столовая Камерона). 1947 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Греческий зал. 1944 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Галерея Гонзаго. 1944 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Библиотека Павла. 1944 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>10. Павловский дворец. Библиотека Павла. 1944 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Кавалерский зал. 1944 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>11. Павловский дворец. Кавалерскй зал. 1944 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вид разрушенного Павловского дворца. 1944 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>12. Вид разрушенного Павловского дворца. 1944 (2)</t>
+  </si>
+  <si>
+    <t>13. Вид разрушенного Павловского дворца. 1944 г.</t>
+  </si>
+  <si>
+    <t>14. Вид разрушенного Павловского дворца. 1944</t>
+  </si>
+  <si>
+    <t>15. Вид разрушенного Павловского дворца. 1944</t>
+  </si>
+  <si>
+    <t>16. Олейник Ф.Ф. Павловский дворец. Разрушенный фасад Центрального корпуса. НВК-12495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Олейник Ф.Ф.
+Павловский дворец. Разрушенный фасад Центрального корпуса. 1944 г.
+НВК-12495
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>17. Мавзолей Павла I. Интерьер. 1944 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мавзолей Павла I. Интерьер. 1944 г.
+Фотография
+Государственный музей-заповедник «Павловск»
 </t>
   </si>
 </sst>
@@ -587,7 +713,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -595,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="40.3671875" customWidth="1"/>
@@ -740,7 +866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="57.6">
+    <row r="17" spans="1:3" ht="57.6">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -748,7 +874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="57.6">
+    <row r="18" spans="1:3" ht="57.6">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -756,7 +882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="72">
+    <row r="19" spans="1:3" ht="72">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -764,7 +890,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="57.6">
+    <row r="20" spans="1:3" ht="57.6">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -772,7 +898,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="72">
+    <row r="21" spans="1:3" ht="72">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -780,12 +906,149 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="72">
+    <row r="22" spans="1:3" ht="72">
       <c r="A22" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>44</v>
+      </c>
+      <c r="C22" s="6"/>
+    </row>
+    <row r="23" spans="1:3" ht="57.6">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="57.6">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="57.6">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="57.6">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="57.6">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="72">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="72">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="72">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="57.6">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="57.6">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="57.6">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="57.6">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="57.6">
+      <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="57.6">
+      <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="57.6">
+      <c r="A37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="86.4">
+      <c r="A38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="57.6">
+      <c r="A39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
